--- a/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M06/third/CF_M06_req_eval.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M06/third/CF_M06_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.3607</v>
       </c>
       <c r="D13" t="n">
+        <v>0.5301</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9191</v>
       </c>
     </row>
@@ -755,14 +763,11 @@
           <t>The system shall allow the user to select a client to view their locations.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -776,10 +781,6 @@
           <t>Partners to consult the list of locations of a previously selected client.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -810,10 +811,6 @@
           <t>The system shall allow the partner to create a new location for a client.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -827,10 +824,6 @@
           <t>Partners to create a new location for a client.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -861,10 +854,6 @@
           <t>The system shall allow the partner to consult the current status of their clients' players.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -878,10 +867,6 @@
           <t>Partners to consult the current status of the different players of their clients.</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -912,14 +897,11 @@
           <t>The system shall integrate with Google Maps API to facilitate address searching.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -933,14 +915,11 @@
           <t>The Google Maps API is used to facilitate address search, making it easier to fill out form fields.</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>CF_M06_R09</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -971,14 +950,11 @@
           <t>The system shall allow the user to filter and sort the client list.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -992,14 +968,11 @@
           <t>The user can filter the list by different criteria and sort the list.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M06_R01</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1030,14 +1003,11 @@
           <t>The system shall display the current status and last connection time for each player in the location list.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1051,14 +1021,11 @@
           <t>In the list of locations of a client, each player displays information about its current status and last connection.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>CF_M06_R15</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1089,10 +1056,6 @@
           <t>The system shall allow the partner to consult the list of their clients.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1106,10 +1069,6 @@
           <t>Partners to consult the list of their clients.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1140,14 +1099,11 @@
           <t>The system shall provide buttons to restart, shut down, force synchronization, and restart playback.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_14</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1161,14 +1117,11 @@
           <t>On the player screen, buttons are displayed for different actions: restart players, turn off, force synchronization, and restart playback.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M06_R17</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1199,10 +1152,6 @@
           <t>The system shall allow the partner to perform real-time actions on a player.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1216,10 +1165,6 @@
           <t>Partners to perform different actions on a player in real time.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1250,14 +1195,11 @@
           <t>The system shall provide a form to create a new location.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_07</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1271,14 +1213,11 @@
           <t>A form is displayed to create a new location.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M06_R09</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1309,10 +1248,6 @@
           <t>The system shall allow the partner to consult the list of locations for a selected client.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1326,14 +1261,11 @@
           <t>The user can select a client and consult the list of locations.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>CF_M06_R01</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1364,10 +1296,6 @@
           <t>The system shall allow the partner to receive push notifications.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1381,10 +1309,6 @@
           <t>Partners to receive push notifications.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1415,14 +1339,11 @@
           <t>The system shall display a list of locations with their respective players.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1436,14 +1357,11 @@
           <t>A list of locations with their respective players is displayed.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M06_R05</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1474,14 +1392,11 @@
           <t>The system shall display a list of clients with basic data.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1495,14 +1410,11 @@
           <t>A list of clients with basic data is displayed.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M06_R01</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1533,10 +1445,6 @@
           <t>The system shall allow the partner to initiate the registration process of a player by scanning a QR code.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1550,10 +1458,6 @@
           <t>Partners to initiate the player registration process by scanning the QR code displayed on the screen.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1584,14 +1488,11 @@
           <t>The system shall send push notifications to the user's device in case of incidents if permissions are enabled.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_16</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1605,14 +1506,11 @@
           <t>If the user has notification permissions enabled, they will receive push notifications on their device in case of incidents.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M06_R32</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1643,14 +1541,11 @@
           <t>If the QR code is valid, the system shall navigate to screens for selecting client and location.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_10</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1664,14 +1559,11 @@
           <t>If the QR code is scanned correctly and is valid, the system navigates to the subsequent screens to select the client and location.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M06_R12</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1702,10 +1594,6 @@
           <t>The application must be compatible with English, French, German, Catalan, Spanish, Portuguese, and Italian.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1729,8 +1617,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1766,9 +1652,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1792,8 +1675,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1829,9 +1710,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>Constraint</t>
@@ -1845,9 +1723,6 @@
           <t>The application must be available for mobile devices with iOS and Android systems.</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr">
         <is>
           <t>Classification Change</t>
@@ -1888,9 +1763,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1914,8 +1786,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1951,9 +1821,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1977,8 +1844,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
